--- a/data/paises_extra/por_pais/Gobernanza_ES_Espana_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Gobernanza_ES_Espana_ILIA2026.xlsx
@@ -597,7 +597,9 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>https://www.lamoncloa.gob.es</t>
+          <t>https://www.lamoncloa.gob.es/consejodeministros/resumenes/paginas/2024/140524-rueda-de-prensa-ministros.aspx
+https://digital.gob.es/comunicacion/notas-prensa/secretaria-digitalizacion-e-inteligencia-artificial/2024/05/2024-05-14.html
+https://www.lamoncloa.gob.es/presidente/actividades/Paginas/2020/021220-sanchezenia.aspx</t>
         </is>
       </c>
     </row>
@@ -629,7 +631,8 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>https://planderecuperacion.gob.es</t>
+          <t>https://www.lamoncloa.gob.es/consejodeministros/resumenes/paginas/2024/140524-rueda-de-prensa-ministros.aspx
+https://planderecuperacion.gob.es/noticias/gobierno-aprueba-estrategia-inteligencia-artificial-2024-prtr</t>
         </is>
       </c>
     </row>
@@ -661,7 +664,8 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>https://planderecuperacion.gob.es</t>
+          <t>https://planderecuperacion.gob.es/noticias/gobierno-aprueba-estrategia-inteligencia-artificial-2024-prtr
+https://planderecuperacion.gob.es/noticias/conoce-Estrategia-Nacional-Inteligencia-Artificial-ENIA-IA-prtr</t>
         </is>
       </c>
     </row>
@@ -693,7 +697,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>https://www.mineco.gob.es</t>
+          <t>https://portal.mineco.gob.es/RecursosNoticia/mineco/prensa/noticias/2023/20230522_informe_enia.pdf</t>
         </is>
       </c>
     </row>
@@ -725,7 +729,8 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>https://planderecuperacion.gob.es</t>
+          <t>https://planderecuperacion.gob.es/noticias/gobierno-aprueba-estrategia-inteligencia-artificial-2024-prtr
+https://www.lamoncloa.gob.es/presidente/actividades/Paginas/2020/021220-sanchezenia.aspx</t>
         </is>
       </c>
     </row>
@@ -757,7 +762,8 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>https://planderecuperacion.gob.es</t>
+          <t>https://digital.gob.es/comunicacion/notas-prensa/secretaria-digitalizacion-e-inteligencia-artificial/2024/05/2024-05-14.html
+https://planderecuperacion.gob.es/noticias/gobierno-aprueba-estrategia-inteligencia-artificial-2024-prtr</t>
         </is>
       </c>
     </row>
@@ -789,7 +795,8 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>https://aesia.digital.gob.es</t>
+          <t>https://aesia.digital.gob.es
+https://digital.gob.es/comunicacion/notas-prensa/mtdfp/2025/03/2025-03-11</t>
         </is>
       </c>
     </row>
@@ -821,7 +828,8 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>https://planderecuperacion.gob.es</t>
+          <t>https://planderecuperacion.gob.es/noticias/gobierno-aprueba-estrategia-inteligencia-artificial-2024-prtr
+https://www.bsc.es/news/bsc-news/alia-europes-first-public-open-and-multilingual-ai-infrastructure</t>
         </is>
       </c>
     </row>
@@ -853,7 +861,8 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>https://planderecuperacion.gob.es</t>
+          <t>https://planderecuperacion.gob.es/noticias/gobierno-aprueba-estrategia-inteligencia-artificial-2024-prtr
+https://aesia.digital.gob.es</t>
         </is>
       </c>
     </row>
@@ -885,7 +894,8 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>https://datos.gob.es</t>
+          <t>https://aesia.digital.gob.es/en/presentalia
+https://www.bsc.es/news/bsc-news/alia-europes-first-public-open-and-multilingual-ai-infrastructure</t>
         </is>
       </c>
     </row>
@@ -917,7 +927,8 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>https://www.lamoncloa.gob.es</t>
+          <t>https://www.lamoncloa.gob.es/consejodeministros/resumenes/paginas/2024/140524-rueda-de-prensa-ministros.aspx
+https://digital.gob.es/comunicacion/notas-prensa/secretaria-digitalizacion-e-inteligencia-artificial/2024/05/2024-05-14.html</t>
         </is>
       </c>
     </row>
@@ -949,7 +960,8 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>https://planderecuperacion.gob.es</t>
+          <t>https://planderecuperacion.gob.es/noticias/gobierno-aprueba-estrategia-inteligencia-artificial-2024-prtr
+https://www.boe.es/diario_boe/txt.php?id=BOE-A-2023-22767</t>
         </is>
       </c>
     </row>
@@ -981,7 +993,8 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>https://www.ciencia.gob.es</t>
+          <t>https://planderecuperacion.gob.es/noticias/gobierno-aprueba-estrategia-inteligencia-artificial-2024-prtr
+https://digital.gob.es/comunicacion/notas-prensa/secretaria-digitalizacion-e-inteligencia-artificial/2024/05/2024-05-14.html</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1026,8 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>https://www.esmartcity.es</t>
+          <t>https://www.boe.es/diario_boe/txt.php?id=BOE-A-2023-22767
+https://oecd.ai/en/ai-principles</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1059,8 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>https://www.clubexcelencia.org</t>
+          <t>https://planderecuperacion.gob.es/noticias/conoce-Estrategia-Nacional-Inteligencia-Artificial-ENIA-IA-prtr
+https://www.lamoncloa.gob.es/presidente/actividades/Paginas/2020/021220-sanchezenia.aspx</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1087,13 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>'Crecimiento sostenible'; Programa Algoritmos Verdes (2022).  [confianza: ALTA]</t>
+          <t>'Crecimiento sostenible'; Programa Nacional de Algoritmos Verdes (2022).  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>https://algoritmosverdes.gob.es</t>
+          <t>https://portal.mineco.gob.es/es-es/comunicacion/Paginas/algoritmos-verdes.aspx
+https://algoritmosverdes.gob.es/es/recursos/programa-nacional-de-algoritmos-verdes</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1125,8 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>https://avance.digital.gob.es</t>
+          <t>https://avance.digital.gob.es/_layouts/15/HttpHandlerParticipacionPublicaAnexos.ashx?k=19128
+https://digital.gob.es/comunicacion/notas-prensa/mtdfp/2025/03/2025-03-11</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1158,8 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>https://www.gtt.es</t>
+          <t>https://planderecuperacion.gob.es/noticias/conoce-Estrategia-Nacional-Inteligencia-Artificial-ENIA-IA-prtr
+https://www.lamoncloa.gob.es/consejodeministros/resumenes/paginas/2024/140524-rueda-de-prensa-ministros.aspx</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1191,8 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>https://www.lamoncloa.gob.es</t>
+          <t>https://www.lamoncloa.gob.es/consejodeministros/resumenes/paginas/2024/140524-rueda-de-prensa-ministros.aspx
+https://digital.gob.es/comunicacion/notas-prensa/secretaria-digitalizacion-e-inteligencia-artificial/2024/05/2024-05-14.html</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1224,8 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>https://www.boe.es</t>
+          <t>https://www.boe.es/buscar/doc.php?id=BOE-A-2023-18911
+https://aesia.digital.gob.es</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1257,8 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>https://www.lamoncloa.gob.es</t>
+          <t>https://www.lamoncloa.gob.es/consejodeministros/resumenes/paginas/2024/140524-rueda-de-prensa-ministros.aspx
+https://portal.mineco.gob.es/RecursosNoticia/mineco/prensa/noticias/2023/20230522_informe_enia.pdf</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1362,7 @@
       <c r="F31" s="6" t="inlineStr">
         <is>
           <t>https://oecd.ai/en/ai-principles
-https://www.boe.es</t>
+https://oecd.ai/en/about/about-gpai</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1401,9 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>https://www.lamoncloa.gob.es</t>
+          <t>https://digital.gob.es/comunicacion/notas-prensa/mtdfp/2025/03/2025-03-11
+https://avance.digital.gob.es/_layouts/15/HttpHandlerParticipacionPublicaAnexos.ashx?k=19128
+https://eur-lex.europa.eu/eli/reg/2024/1689/oj</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1435,8 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>https://aesia.digital.gob.es</t>
+          <t>https://aesia.digital.gob.es
+https://eur-lex.europa.eu/eli/reg/2024/1689/oj</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1463,12 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>1er sandbox de IA de la UE (2022→jun-2026; ~€4,3M; 44 solicitudes).  [confianza: ALTA]</t>
+          <t>1er sandbox de IA de la UE (RD 817/2023; 2022→jun-2026; ~€4,3M; 44 solicitudes).  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>https://portal.mineco.gob.es</t>
+          <t>https://www.boe.es/diario_boe/txt.php?id=BOE-A-2023-22767</t>
         </is>
       </c>
     </row>

--- a/data/paises_extra/por_pais/Gobernanza_ES_Espana_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Gobernanza_ES_Espana_ILIA2026.xlsx
@@ -525,7 +525,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Compendio exhaustivo de URLs: gobernanza/FUENTES_gobernanza_EE_SG.md (EE/SG) · gobernanza_&lt;país&gt;.md, gobernanza_estandares_*.md, etica_seguridad_*.md, energia_*.md (DE/ES/PT). Rúbricas: gobernanza/RUBRICAS_gobernanza.md.</t>
+          <t>Cada URL va etiquetada [oficial] (gobierno, BOE/Diário da República, ISO/ITU, OCDE, dato primario) o [secundaria] (prensa, despacho, agregador). Compendio exhaustivo: gobernanza/FUENTES_gobernanza_EE_SG.md (EE/SG) · gobernanza_&lt;país&gt;.md, gobernanza_estandares_*.md, etica_seguridad_*.md, energia_*.md (DE/ES/PT). Rúbricas: gobernanza/RUBRICAS_gobernanza.md.</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Fuentes y URLs</t>
+          <t>Fuentes y URLs  ([oficial] primaria · [secundaria] corrobora)</t>
         </is>
       </c>
     </row>
@@ -597,9 +597,9 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>https://www.lamoncloa.gob.es/consejodeministros/resumenes/paginas/2024/140524-rueda-de-prensa-ministros.aspx
-https://digital.gob.es/comunicacion/notas-prensa/secretaria-digitalizacion-e-inteligencia-artificial/2024/05/2024-05-14.html
-https://www.lamoncloa.gob.es/presidente/actividades/Paginas/2020/021220-sanchezenia.aspx</t>
+          <t>[oficial] https://www.lamoncloa.gob.es/consejodeministros/resumenes/paginas/2024/140524-rueda-de-prensa-ministros.aspx
+[oficial] https://digital.gob.es/comunicacion/notas-prensa/secretaria-digitalizacion-e-inteligencia-artificial/2024/05/2024-05-14.html
+[oficial] https://www.lamoncloa.gob.es/presidente/actividades/Paginas/2020/021220-sanchezenia.aspx</t>
         </is>
       </c>
     </row>
@@ -631,8 +631,8 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>https://www.lamoncloa.gob.es/consejodeministros/resumenes/paginas/2024/140524-rueda-de-prensa-ministros.aspx
-https://planderecuperacion.gob.es/noticias/gobierno-aprueba-estrategia-inteligencia-artificial-2024-prtr</t>
+          <t>[oficial] https://www.lamoncloa.gob.es/consejodeministros/resumenes/paginas/2024/140524-rueda-de-prensa-ministros.aspx
+[oficial] https://planderecuperacion.gob.es/noticias/gobierno-aprueba-estrategia-inteligencia-artificial-2024-prtr</t>
         </is>
       </c>
     </row>
@@ -664,8 +664,8 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>https://planderecuperacion.gob.es/noticias/gobierno-aprueba-estrategia-inteligencia-artificial-2024-prtr
-https://planderecuperacion.gob.es/noticias/conoce-Estrategia-Nacional-Inteligencia-Artificial-ENIA-IA-prtr</t>
+          <t>[oficial] https://planderecuperacion.gob.es/noticias/gobierno-aprueba-estrategia-inteligencia-artificial-2024-prtr
+[oficial] https://planderecuperacion.gob.es/noticias/conoce-Estrategia-Nacional-Inteligencia-Artificial-ENIA-IA-prtr</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,8 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>https://portal.mineco.gob.es/RecursosNoticia/mineco/prensa/noticias/2023/20230522_informe_enia.pdf</t>
+          <t>[oficial] https://portal.mineco.gob.es/RecursosNoticia/mineco/prensa/noticias/2023/20230522_informe_enia.pdf
+[oficial] https://www.lamoncloa.gob.es/consejodeministros/resumenes/paginas/2024/140524-rueda-de-prensa-ministros.aspx</t>
         </is>
       </c>
     </row>
@@ -729,8 +730,8 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>https://planderecuperacion.gob.es/noticias/gobierno-aprueba-estrategia-inteligencia-artificial-2024-prtr
-https://www.lamoncloa.gob.es/presidente/actividades/Paginas/2020/021220-sanchezenia.aspx</t>
+          <t>[oficial] https://planderecuperacion.gob.es/noticias/gobierno-aprueba-estrategia-inteligencia-artificial-2024-prtr
+[oficial] https://www.lamoncloa.gob.es/presidente/actividades/Paginas/2020/021220-sanchezenia.aspx</t>
         </is>
       </c>
     </row>
@@ -762,8 +763,8 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>https://digital.gob.es/comunicacion/notas-prensa/secretaria-digitalizacion-e-inteligencia-artificial/2024/05/2024-05-14.html
-https://planderecuperacion.gob.es/noticias/gobierno-aprueba-estrategia-inteligencia-artificial-2024-prtr</t>
+          <t>[oficial] https://digital.gob.es/comunicacion/notas-prensa/secretaria-digitalizacion-e-inteligencia-artificial/2024/05/2024-05-14.html
+[oficial] https://planderecuperacion.gob.es/noticias/gobierno-aprueba-estrategia-inteligencia-artificial-2024-prtr</t>
         </is>
       </c>
     </row>
@@ -795,8 +796,8 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>https://aesia.digital.gob.es
-https://digital.gob.es/comunicacion/notas-prensa/mtdfp/2025/03/2025-03-11</t>
+          <t>[oficial] https://aesia.digital.gob.es
+[oficial] https://digital.gob.es/comunicacion/notas-prensa/mtdfp/2025/03/2025-03-11</t>
         </is>
       </c>
     </row>
@@ -828,8 +829,8 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>https://planderecuperacion.gob.es/noticias/gobierno-aprueba-estrategia-inteligencia-artificial-2024-prtr
-https://www.bsc.es/news/bsc-news/alia-europes-first-public-open-and-multilingual-ai-infrastructure</t>
+          <t>[oficial] https://planderecuperacion.gob.es/noticias/gobierno-aprueba-estrategia-inteligencia-artificial-2024-prtr
+[oficial] https://www.bsc.es/news/bsc-news/alia-europes-first-public-open-and-multilingual-ai-infrastructure</t>
         </is>
       </c>
     </row>
@@ -861,8 +862,8 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>https://planderecuperacion.gob.es/noticias/gobierno-aprueba-estrategia-inteligencia-artificial-2024-prtr
-https://aesia.digital.gob.es</t>
+          <t>[oficial] https://planderecuperacion.gob.es/noticias/gobierno-aprueba-estrategia-inteligencia-artificial-2024-prtr
+[oficial] https://aesia.digital.gob.es</t>
         </is>
       </c>
     </row>
@@ -894,8 +895,8 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>https://aesia.digital.gob.es/en/presentalia
-https://www.bsc.es/news/bsc-news/alia-europes-first-public-open-and-multilingual-ai-infrastructure</t>
+          <t>[oficial] https://aesia.digital.gob.es/en/presentalia
+[oficial] https://www.bsc.es/news/bsc-news/alia-europes-first-public-open-and-multilingual-ai-infrastructure</t>
         </is>
       </c>
     </row>
@@ -927,8 +928,8 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>https://www.lamoncloa.gob.es/consejodeministros/resumenes/paginas/2024/140524-rueda-de-prensa-ministros.aspx
-https://digital.gob.es/comunicacion/notas-prensa/secretaria-digitalizacion-e-inteligencia-artificial/2024/05/2024-05-14.html</t>
+          <t>[oficial] https://www.lamoncloa.gob.es/consejodeministros/resumenes/paginas/2024/140524-rueda-de-prensa-ministros.aspx
+[oficial] https://digital.gob.es/comunicacion/notas-prensa/secretaria-digitalizacion-e-inteligencia-artificial/2024/05/2024-05-14.html</t>
         </is>
       </c>
     </row>
@@ -960,8 +961,8 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>https://planderecuperacion.gob.es/noticias/gobierno-aprueba-estrategia-inteligencia-artificial-2024-prtr
-https://www.boe.es/diario_boe/txt.php?id=BOE-A-2023-22767</t>
+          <t>[oficial] https://planderecuperacion.gob.es/noticias/gobierno-aprueba-estrategia-inteligencia-artificial-2024-prtr
+[oficial] https://www.boe.es/diario_boe/txt.php?id=BOE-A-2023-22767</t>
         </is>
       </c>
     </row>
@@ -993,8 +994,8 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>https://planderecuperacion.gob.es/noticias/gobierno-aprueba-estrategia-inteligencia-artificial-2024-prtr
-https://digital.gob.es/comunicacion/notas-prensa/secretaria-digitalizacion-e-inteligencia-artificial/2024/05/2024-05-14.html</t>
+          <t>[oficial] https://planderecuperacion.gob.es/noticias/gobierno-aprueba-estrategia-inteligencia-artificial-2024-prtr
+[oficial] https://digital.gob.es/comunicacion/notas-prensa/secretaria-digitalizacion-e-inteligencia-artificial/2024/05/2024-05-14.html</t>
         </is>
       </c>
     </row>
@@ -1026,8 +1027,8 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>https://www.boe.es/diario_boe/txt.php?id=BOE-A-2023-22767
-https://oecd.ai/en/ai-principles</t>
+          <t>[oficial] https://www.boe.es/diario_boe/txt.php?id=BOE-A-2023-22767
+[oficial] https://oecd.ai/en/ai-principles</t>
         </is>
       </c>
     </row>
@@ -1059,8 +1060,8 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>https://planderecuperacion.gob.es/noticias/conoce-Estrategia-Nacional-Inteligencia-Artificial-ENIA-IA-prtr
-https://www.lamoncloa.gob.es/presidente/actividades/Paginas/2020/021220-sanchezenia.aspx</t>
+          <t>[oficial] https://planderecuperacion.gob.es/noticias/conoce-Estrategia-Nacional-Inteligencia-Artificial-ENIA-IA-prtr
+[oficial] https://www.lamoncloa.gob.es/presidente/actividades/Paginas/2020/021220-sanchezenia.aspx</t>
         </is>
       </c>
     </row>
@@ -1092,8 +1093,8 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>https://portal.mineco.gob.es/es-es/comunicacion/Paginas/algoritmos-verdes.aspx
-https://algoritmosverdes.gob.es/es/recursos/programa-nacional-de-algoritmos-verdes</t>
+          <t>[oficial] https://portal.mineco.gob.es/es-es/comunicacion/Paginas/algoritmos-verdes.aspx
+[oficial] https://algoritmosverdes.gob.es/es/recursos/programa-nacional-de-algoritmos-verdes</t>
         </is>
       </c>
     </row>
@@ -1125,8 +1126,8 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>https://avance.digital.gob.es/_layouts/15/HttpHandlerParticipacionPublicaAnexos.ashx?k=19128
-https://digital.gob.es/comunicacion/notas-prensa/mtdfp/2025/03/2025-03-11</t>
+          <t>[oficial] https://avance.digital.gob.es/_layouts/15/HttpHandlerParticipacionPublicaAnexos.ashx?k=19128
+[oficial] https://digital.gob.es/comunicacion/notas-prensa/mtdfp/2025/03/2025-03-11</t>
         </is>
       </c>
     </row>
@@ -1158,8 +1159,8 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>https://planderecuperacion.gob.es/noticias/conoce-Estrategia-Nacional-Inteligencia-Artificial-ENIA-IA-prtr
-https://www.lamoncloa.gob.es/consejodeministros/resumenes/paginas/2024/140524-rueda-de-prensa-ministros.aspx</t>
+          <t>[oficial] https://planderecuperacion.gob.es/noticias/conoce-Estrategia-Nacional-Inteligencia-Artificial-ENIA-IA-prtr
+[oficial] https://www.lamoncloa.gob.es/consejodeministros/resumenes/paginas/2024/140524-rueda-de-prensa-ministros.aspx</t>
         </is>
       </c>
     </row>
@@ -1191,8 +1192,8 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>https://www.lamoncloa.gob.es/consejodeministros/resumenes/paginas/2024/140524-rueda-de-prensa-ministros.aspx
-https://digital.gob.es/comunicacion/notas-prensa/secretaria-digitalizacion-e-inteligencia-artificial/2024/05/2024-05-14.html</t>
+          <t>[oficial] https://www.lamoncloa.gob.es/consejodeministros/resumenes/paginas/2024/140524-rueda-de-prensa-ministros.aspx
+[oficial] https://digital.gob.es/comunicacion/notas-prensa/secretaria-digitalizacion-e-inteligencia-artificial/2024/05/2024-05-14.html</t>
         </is>
       </c>
     </row>
@@ -1224,8 +1225,8 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>https://www.boe.es/buscar/doc.php?id=BOE-A-2023-18911
-https://aesia.digital.gob.es</t>
+          <t>[oficial] https://www.boe.es/buscar/doc.php?id=BOE-A-2023-18911
+[oficial] https://aesia.digital.gob.es</t>
         </is>
       </c>
     </row>
@@ -1257,8 +1258,8 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>https://www.lamoncloa.gob.es/consejodeministros/resumenes/paginas/2024/140524-rueda-de-prensa-ministros.aspx
-https://portal.mineco.gob.es/RecursosNoticia/mineco/prensa/noticias/2023/20230522_informe_enia.pdf</t>
+          <t>[oficial] https://www.lamoncloa.gob.es/consejodeministros/resumenes/paginas/2024/140524-rueda-de-prensa-ministros.aspx
+[oficial] https://portal.mineco.gob.es/RecursosNoticia/mineco/prensa/noticias/2023/20230522_informe_enia.pdf</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1298,8 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>https://www.iso.org/committee/6794475.html?view=participation</t>
+          <t>[oficial] https://www.iso.org/committee/6794475.html?view=participation
+[secundaria] https://jtc1info.org/sd-2-history/jtc1-subcommittees/sc-42/</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1331,8 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>https://www.iso.org/committee/45306.html?view=participation</t>
+          <t>[oficial] https://www.iso.org/committee/45306.html?view=participation
+[secundaria] https://en.wikipedia.org/wiki/ISO/IEC_JTC_1/SC_27</t>
         </is>
       </c>
     </row>
@@ -1361,8 +1364,8 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>https://oecd.ai/en/ai-principles
-https://oecd.ai/en/about/about-gpai</t>
+          <t>[oficial] https://oecd.ai/en/ai-principles
+[oficial] https://oecd.ai/en/about/about-gpai</t>
         </is>
       </c>
     </row>
@@ -1401,9 +1404,9 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>https://digital.gob.es/comunicacion/notas-prensa/mtdfp/2025/03/2025-03-11
-https://avance.digital.gob.es/_layouts/15/HttpHandlerParticipacionPublicaAnexos.ashx?k=19128
-https://eur-lex.europa.eu/eli/reg/2024/1689/oj</t>
+          <t>[oficial] https://digital.gob.es/comunicacion/notas-prensa/mtdfp/2025/03/2025-03-11
+[oficial] https://avance.digital.gob.es/_layouts/15/HttpHandlerParticipacionPublicaAnexos.ashx?k=19128
+[oficial] https://eur-lex.europa.eu/eli/reg/2024/1689/oj</t>
         </is>
       </c>
     </row>
@@ -1435,8 +1438,8 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>https://aesia.digital.gob.es
-https://eur-lex.europa.eu/eli/reg/2024/1689/oj</t>
+          <t>[oficial] https://aesia.digital.gob.es
+[oficial] https://eur-lex.europa.eu/eli/reg/2024/1689/oj</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1471,8 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>https://www.boe.es/diario_boe/txt.php?id=BOE-A-2023-22767</t>
+          <t>[oficial] https://www.boe.es/diario_boe/txt.php?id=BOE-A-2023-22767
+[secundaria] https://artificialintelligenceact.eu/ai-regulatory-sandbox-approaches-eu-member-state-overview/</t>
         </is>
       </c>
     </row>
@@ -1500,8 +1504,8 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>https://www.dlapiperdataprotection.com/?t=law&amp;c=ES
-https://www.aepd.es</t>
+          <t>[oficial] https://www.aepd.es
+[secundaria] https://www.dlapiperdataprotection.com/?t=law&amp;c=ES</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1537,8 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>https://www.aepd.es</t>
+          <t>[oficial] https://www.aepd.es
+[secundaria] https://www.dlapiperdataprotection.com/?t=authority&amp;c=ES</t>
         </is>
       </c>
     </row>
@@ -1572,8 +1577,8 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>https://espanadigital.gob.es
-https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
+          <t>[oficial] https://espanadigital.gob.es
+[oficial] https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
         </is>
       </c>
     </row>
@@ -1605,8 +1610,8 @@
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>https://espanadigital.gob.es
-https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
+          <t>[oficial] https://espanadigital.gob.es
+[oficial] https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
         </is>
       </c>
     </row>
@@ -1638,8 +1643,8 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>https://espanadigital.gob.es
-https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
+          <t>[oficial] https://espanadigital.gob.es
+[oficial] https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
         </is>
       </c>
     </row>
@@ -1671,8 +1676,8 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>https://espanadigital.gob.es
-https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
+          <t>[oficial] https://espanadigital.gob.es
+[oficial] https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
         </is>
       </c>
     </row>
@@ -1704,8 +1709,8 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>https://espanadigital.gob.es
-https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
+          <t>[oficial] https://espanadigital.gob.es
+[oficial] https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1742,8 @@
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>https://www.global-index.ai</t>
+          <t>[oficial] https://www.global-index.ai
+[secundaria] https://girai-report-2024-corrected-edition.tiiny.site/</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1775,8 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>https://www.global-index.ai</t>
+          <t>[oficial] https://www.global-index.ai
+[oficial] https://www.globalcenter.ai/</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1808,8 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>https://networkreadinessindex.org/country/spain/</t>
+          <t>[oficial] https://networkreadinessindex.org/country/spain/
+[oficial] https://download.networkreadinessindex.org/reports/countries/2025/spain.pdf</t>
         </is>
       </c>
     </row>
@@ -1833,8 +1841,8 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/owid/energy-data/master/owid-energy-data.csv
-https://ember-energy.org/data/electricity-data-explorer/</t>
+          <t>[oficial] https://raw.githubusercontent.com/owid/energy-data/master/owid-energy-data.csv
+[oficial] https://ember-energy.org/data/electricity-data-explorer/</t>
         </is>
       </c>
     </row>

--- a/data/paises_extra/por_pais/Gobernanza_ES_Espana_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Gobernanza_ES_Espana_ILIA2026.xlsx
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -1836,13 +1836,13 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>57,34 % (2024) / 55,86 % (2025) renovable total. Excl. toda hidro 45,09 %; hidro 12,25 % → si ILIA excluyera gran hidro, baja bastante.  [confianza: ALTA]</t>
+          <t>Energía limpia 2025 = 74,65 % = renovables 55,86 % + NUCLEAR 18,79 % (incl. hidro 11,38 %). EMBER, determinístico ((160,86+54,10)/287,97 TWh). A confirmar con CENIA.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>[oficial] https://raw.githubusercontent.com/owid/energy-data/master/owid-energy-data.csv
-[oficial] https://ember-energy.org/data/electricity-data-explorer/</t>
+          <t>[oficial] https://ember-energy.org/data/electricity-data-explorer/
+[oficial] https://raw.githubusercontent.com/owid/energy-data/master/owid-energy-data.csv</t>
         </is>
       </c>
     </row>
